--- a/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
+++ b/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
@@ -427,7 +427,7 @@
         <v>Passed Tests</v>
       </c>
       <c r="B3">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>Failed Tests</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B5" t="str">
-        <v>99%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>Deployable Status</v>
       </c>
       <c r="B6" t="str">
-        <v>REQUIRES FIXES ❌</v>
+        <v>READY FOR DEPLOYMENT ✅</v>
       </c>
     </row>
     <row r="8">
@@ -475,7 +475,7 @@
         <v>Validation Tests</v>
       </c>
       <c r="B10" t="str">
-        <v>43/44 Passed</v>
+        <v>44/44 Passed</v>
       </c>
     </row>
     <row r="11">
@@ -521,7 +521,7 @@
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>1313 ms</v>
+        <v>1391 ms</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +532,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>1028 ms</v>
+        <v>1042 ms</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>967 ms</v>
+        <v>950 ms</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>957 ms</v>
+        <v>1055 ms</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>954 ms</v>
+        <v>966 ms</v>
       </c>
     </row>
     <row r="7">
@@ -576,7 +576,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>962 ms</v>
+        <v>950 ms</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>962 ms</v>
+        <v>949 ms</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>968 ms</v>
+        <v>970 ms</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>963 ms</v>
+        <v>966 ms</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>984 ms</v>
+        <v>966 ms</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +642,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>960 ms</v>
+        <v>958 ms</v>
       </c>
     </row>
     <row r="14">
@@ -653,7 +653,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>984 ms</v>
+        <v>962 ms</v>
       </c>
     </row>
     <row r="15">
@@ -664,7 +664,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>963 ms</v>
+        <v>979 ms</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>962 ms</v>
+        <v>970 ms</v>
       </c>
     </row>
     <row r="17">
@@ -686,7 +686,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>989 ms</v>
+        <v>968 ms</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>954 ms</v>
+        <v>966 ms</v>
       </c>
     </row>
     <row r="19">
@@ -708,7 +708,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>971 ms</v>
+        <v>972 ms</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>989 ms</v>
+        <v>979 ms</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>974 ms</v>
+        <v>978 ms</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>962 ms</v>
+        <v>992 ms</v>
       </c>
     </row>
     <row r="23">
@@ -752,7 +752,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>961 ms</v>
+        <v>959 ms</v>
       </c>
     </row>
     <row r="24">
@@ -763,7 +763,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>967 ms</v>
+        <v>961 ms</v>
       </c>
     </row>
     <row r="25">
@@ -774,7 +774,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>943 ms</v>
+        <v>947 ms</v>
       </c>
     </row>
     <row r="26">
@@ -785,7 +785,7 @@
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>1479 ms</v>
+        <v>1443 ms</v>
       </c>
     </row>
     <row r="27">
@@ -796,7 +796,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>29 ms</v>
+        <v>49 ms</v>
       </c>
     </row>
     <row r="28">
@@ -807,7 +807,7 @@
         <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>9 ms</v>
+        <v>6 ms</v>
       </c>
     </row>
     <row r="29">
@@ -818,7 +818,7 @@
         <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>5 ms</v>
+        <v>7 ms</v>
       </c>
     </row>
     <row r="30">
@@ -829,7 +829,7 @@
         <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>4 ms</v>
+        <v>5 ms</v>
       </c>
     </row>
     <row r="31">
@@ -840,7 +840,7 @@
         <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>4 ms</v>
+        <v>5 ms</v>
       </c>
     </row>
     <row r="32">
@@ -851,7 +851,7 @@
         <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>11 ms</v>
+        <v>5 ms</v>
       </c>
     </row>
     <row r="33">
@@ -862,7 +862,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>3 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="34">
@@ -873,7 +873,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>3 ms</v>
+        <v>6 ms</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>22 ms</v>
+        <v>37 ms</v>
       </c>
     </row>
     <row r="36">
@@ -895,7 +895,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>61 ms</v>
+        <v>87 ms</v>
       </c>
     </row>
     <row r="37">
@@ -906,7 +906,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>16 ms</v>
+        <v>34 ms</v>
       </c>
     </row>
     <row r="38">
@@ -917,7 +917,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>1 ms</v>
+        <v>2 ms</v>
       </c>
     </row>
     <row r="39">
@@ -928,7 +928,7 @@
         <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1 ms</v>
+        <v>2 ms</v>
       </c>
     </row>
     <row r="40">
@@ -939,7 +939,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>0 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="42">
@@ -972,7 +972,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>0 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="44">
@@ -983,7 +983,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>1 ms</v>
+        <v>2 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>2129 ms</v>
+        <v>979 ms</v>
       </c>
     </row>
     <row r="3">
@@ -1032,7 +1032,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>1277 ms</v>
+        <v>673 ms</v>
       </c>
     </row>
     <row r="4">
@@ -1043,7 +1043,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>1238 ms</v>
+        <v>649 ms</v>
       </c>
     </row>
     <row r="5">
@@ -1054,7 +1054,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>1036 ms</v>
+        <v>616 ms</v>
       </c>
     </row>
     <row r="6">
@@ -1065,7 +1065,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>1077 ms</v>
+        <v>685 ms</v>
       </c>
     </row>
     <row r="7">
@@ -1076,7 +1076,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>1284 ms</v>
+        <v>683 ms</v>
       </c>
     </row>
     <row r="8">
@@ -1087,7 +1087,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>1232 ms</v>
+        <v>694 ms</v>
       </c>
     </row>
     <row r="9">
@@ -1098,7 +1098,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>1477 ms</v>
+        <v>1084 ms</v>
       </c>
     </row>
     <row r="10">
@@ -1109,7 +1109,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>1243 ms</v>
+        <v>971 ms</v>
       </c>
     </row>
     <row r="11">
@@ -1120,7 +1120,7 @@
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>2199 ms</v>
+        <v>1164 ms</v>
       </c>
     </row>
     <row r="12">
@@ -1131,7 +1131,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>1403 ms</v>
+        <v>1007 ms</v>
       </c>
     </row>
     <row r="13">
@@ -1142,7 +1142,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>1240 ms</v>
+        <v>1125 ms</v>
       </c>
     </row>
     <row r="14">
@@ -1153,7 +1153,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>846 ms</v>
+        <v>911 ms</v>
       </c>
     </row>
     <row r="15">
@@ -1164,7 +1164,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>1021 ms</v>
+        <v>942 ms</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>1524 ms</v>
+        <v>1008 ms</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1186,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>870 ms</v>
+        <v>872 ms</v>
       </c>
     </row>
     <row r="18">
@@ -1197,7 +1197,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>1583 ms</v>
+        <v>1094 ms</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>1216 ms</v>
+        <v>785 ms</v>
       </c>
     </row>
     <row r="20">
@@ -1219,7 +1219,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>906 ms</v>
+        <v>915 ms</v>
       </c>
     </row>
     <row r="21">
@@ -1230,7 +1230,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>892 ms</v>
+        <v>978 ms</v>
       </c>
     </row>
     <row r="22">
@@ -1241,7 +1241,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>1185 ms</v>
+        <v>1112 ms</v>
       </c>
     </row>
     <row r="23">
@@ -1252,7 +1252,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>1097 ms</v>
+        <v>948 ms</v>
       </c>
     </row>
     <row r="24">
@@ -1263,7 +1263,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>1093 ms</v>
+        <v>1054 ms</v>
       </c>
     </row>
     <row r="25">
@@ -1274,7 +1274,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>1188 ms</v>
+        <v>938 ms</v>
       </c>
     </row>
     <row r="26">
@@ -1282,10 +1282,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: empty email should prevent login with empty email</v>
       </c>
       <c r="B26" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>10573 ms</v>
+        <v>415 ms</v>
       </c>
     </row>
     <row r="27">
@@ -1296,7 +1296,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>585 ms</v>
+        <v>573 ms</v>
       </c>
     </row>
     <row r="28">
@@ -1307,7 +1307,7 @@
         <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>535 ms</v>
+        <v>436 ms</v>
       </c>
     </row>
     <row r="29">
@@ -1318,7 +1318,7 @@
         <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>402 ms</v>
+        <v>801 ms</v>
       </c>
     </row>
     <row r="30">
@@ -1329,7 +1329,7 @@
         <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>614 ms</v>
+        <v>646 ms</v>
       </c>
     </row>
     <row r="31">
@@ -1340,7 +1340,7 @@
         <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>599 ms</v>
+        <v>653 ms</v>
       </c>
     </row>
     <row r="32">
@@ -1351,7 +1351,7 @@
         <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>466 ms</v>
+        <v>888 ms</v>
       </c>
     </row>
     <row r="33">
@@ -1362,7 +1362,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>1234 ms</v>
+        <v>1174 ms</v>
       </c>
     </row>
     <row r="34">
@@ -1373,7 +1373,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>956 ms</v>
+        <v>927 ms</v>
       </c>
     </row>
     <row r="35">
@@ -1384,7 +1384,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>958 ms</v>
+        <v>957 ms</v>
       </c>
     </row>
     <row r="36">
@@ -1395,7 +1395,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>1093 ms</v>
+        <v>1105 ms</v>
       </c>
     </row>
     <row r="37">
@@ -1406,7 +1406,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>1285 ms</v>
+        <v>1348 ms</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1417,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>1134 ms</v>
+        <v>1135 ms</v>
       </c>
     </row>
     <row r="39">
@@ -1428,7 +1428,7 @@
         <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1213 ms</v>
+        <v>1353 ms</v>
       </c>
     </row>
     <row r="40">
@@ -1439,7 +1439,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>1152 ms</v>
+        <v>1188 ms</v>
       </c>
     </row>
     <row r="41">
@@ -1450,7 +1450,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1192 ms</v>
+        <v>1253 ms</v>
       </c>
     </row>
     <row r="42">
@@ -1461,7 +1461,7 @@
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>1170 ms</v>
+        <v>1240 ms</v>
       </c>
     </row>
     <row r="43">
@@ -1472,7 +1472,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>1194 ms</v>
+        <v>1277 ms</v>
       </c>
     </row>
     <row r="44">
@@ -1483,7 +1483,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>1186 ms</v>
+        <v>1261 ms</v>
       </c>
     </row>
     <row r="45">
@@ -1494,7 +1494,7 @@
         <v>PASSED</v>
       </c>
       <c r="C45" t="str">
-        <v>1181 ms</v>
+        <v>1266 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1526,772 +1526,772 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
       </c>
       <c r="B2" t="str">
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>2965 ms</v>
+        <v>1380 ms</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
       </c>
       <c r="B3" t="str">
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>2598 ms</v>
+        <v>1425 ms</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
       </c>
       <c r="B4" t="str">
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>2630 ms</v>
+        <v>1718 ms</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
       </c>
       <c r="B5" t="str">
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>2641 ms</v>
+        <v>1620 ms</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
       </c>
       <c r="B6" t="str">
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>2800 ms</v>
+        <v>1779 ms</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
       </c>
       <c r="B7" t="str">
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>2755 ms</v>
+        <v>1663 ms</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
       </c>
       <c r="B8" t="str">
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>2542 ms</v>
+        <v>1464 ms</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
       </c>
       <c r="B9" t="str">
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>2668 ms</v>
+        <v>1686 ms</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
       </c>
       <c r="B10" t="str">
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>2719 ms</v>
+        <v>1607 ms</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
       </c>
       <c r="B11" t="str">
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>2719 ms</v>
+        <v>1474 ms</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
       </c>
       <c r="B12" t="str">
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>2864 ms</v>
+        <v>1481 ms</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
       </c>
       <c r="B13" t="str">
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>2761 ms</v>
+        <v>1617 ms</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
       </c>
       <c r="B14" t="str">
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>2641 ms</v>
+        <v>1664 ms</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
       </c>
       <c r="B15" t="str">
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>2700 ms</v>
+        <v>1443 ms</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
       </c>
       <c r="B16" t="str">
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>2795 ms</v>
+        <v>1431 ms</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
       </c>
       <c r="B17" t="str">
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>1752 ms</v>
+        <v>1483 ms</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
       </c>
       <c r="B18" t="str">
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>1547 ms</v>
+        <v>1612 ms</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
       </c>
       <c r="B19" t="str">
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>2102 ms</v>
+        <v>1430 ms</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
       </c>
       <c r="B20" t="str">
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>2332 ms</v>
+        <v>1651 ms</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
       </c>
       <c r="B21" t="str">
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>1933 ms</v>
+        <v>1659 ms</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
       </c>
       <c r="B22" t="str">
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>1667 ms</v>
+        <v>1606 ms</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
       </c>
       <c r="B23" t="str">
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>2725 ms</v>
+        <v>1621 ms</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
       </c>
       <c r="B24" t="str">
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>2594 ms</v>
+        <v>1433 ms</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
       </c>
       <c r="B25" t="str">
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>1929 ms</v>
+        <v>1446 ms</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
       </c>
       <c r="B26" t="str">
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>1765 ms</v>
+        <v>1455 ms</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
       </c>
       <c r="B27" t="str">
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>1797 ms</v>
+        <v>2636 ms</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
       </c>
       <c r="B28" t="str">
         <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>1642 ms</v>
+        <v>2562 ms</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
       </c>
       <c r="B29" t="str">
         <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>1550 ms</v>
+        <v>2620 ms</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
       </c>
       <c r="B30" t="str">
         <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>2007 ms</v>
+        <v>2585 ms</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
       </c>
       <c r="B31" t="str">
         <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>1768 ms</v>
+        <v>2559 ms</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
       </c>
       <c r="B32" t="str">
         <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>1886 ms</v>
+        <v>2787 ms</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
       </c>
       <c r="B33" t="str">
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>1739 ms</v>
+        <v>2567 ms</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
       </c>
       <c r="B34" t="str">
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>2035 ms</v>
+        <v>2650 ms</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
       </c>
       <c r="B35" t="str">
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>1948 ms</v>
+        <v>2611 ms</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
       </c>
       <c r="B36" t="str">
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>1810 ms</v>
+        <v>2590 ms</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
       </c>
       <c r="B37" t="str">
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>1988 ms</v>
+        <v>2544 ms</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
       </c>
       <c r="B38" t="str">
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>2000 ms</v>
+        <v>2748 ms</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
       </c>
       <c r="B39" t="str">
         <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1831 ms</v>
+        <v>2484 ms</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
       </c>
       <c r="B40" t="str">
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>2173 ms</v>
+        <v>2501 ms</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
       </c>
       <c r="B41" t="str">
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1745 ms</v>
+        <v>2477 ms</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
+        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
       </c>
       <c r="B42" t="str">
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>741 ms</v>
+        <v>12589 ms</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
+        <v>Projects &amp; Kanban should create, filter, and view project details</v>
       </c>
       <c r="B43" t="str">
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>682 ms</v>
+        <v>6406 ms</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
+        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
       </c>
       <c r="B44" t="str">
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>715 ms</v>
+        <v>774 ms</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
+        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
       </c>
       <c r="B45" t="str">
         <v>PASSED</v>
       </c>
       <c r="C45" t="str">
-        <v>928 ms</v>
+        <v>734 ms</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
+        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
       </c>
       <c r="B46" t="str">
         <v>PASSED</v>
       </c>
       <c r="C46" t="str">
-        <v>691 ms</v>
+        <v>1062 ms</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
+        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
       </c>
       <c r="B47" t="str">
         <v>PASSED</v>
       </c>
       <c r="C47" t="str">
-        <v>737 ms</v>
+        <v>813 ms</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
+        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
       </c>
       <c r="B48" t="str">
         <v>PASSED</v>
       </c>
       <c r="C48" t="str">
-        <v>718 ms</v>
+        <v>855 ms</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
+        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
       </c>
       <c r="B49" t="str">
         <v>PASSED</v>
       </c>
       <c r="C49" t="str">
-        <v>746 ms</v>
+        <v>1098 ms</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
+        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
       </c>
       <c r="B50" t="str">
         <v>PASSED</v>
       </c>
       <c r="C50" t="str">
-        <v>714 ms</v>
+        <v>855 ms</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
+        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
       </c>
       <c r="B51" t="str">
         <v>PASSED</v>
       </c>
       <c r="C51" t="str">
-        <v>746 ms</v>
+        <v>1412 ms</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
       </c>
       <c r="B52" t="str">
         <v>PASSED</v>
       </c>
       <c r="C52" t="str">
-        <v>710 ms</v>
+        <v>1035 ms</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
       </c>
       <c r="B53" t="str">
         <v>PASSED</v>
       </c>
       <c r="C53" t="str">
-        <v>710 ms</v>
+        <v>1180 ms</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
+        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
       </c>
       <c r="B54" t="str">
         <v>PASSED</v>
       </c>
       <c r="C54" t="str">
-        <v>804 ms</v>
+        <v>985 ms</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
+        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
       </c>
       <c r="B55" t="str">
         <v>PASSED</v>
       </c>
       <c r="C55" t="str">
-        <v>693 ms</v>
+        <v>869 ms</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
+        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
       </c>
       <c r="B56" t="str">
         <v>PASSED</v>
       </c>
       <c r="C56" t="str">
-        <v>708 ms</v>
+        <v>2238 ms</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
+        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
       </c>
       <c r="B57" t="str">
         <v>PASSED</v>
       </c>
       <c r="C57" t="str">
-        <v>721 ms</v>
+        <v>932 ms</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
+        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
       </c>
       <c r="B58" t="str">
         <v>PASSED</v>
       </c>
       <c r="C58" t="str">
-        <v>708 ms</v>
+        <v>844 ms</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
+        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
       </c>
       <c r="B59" t="str">
         <v>PASSED</v>
       </c>
       <c r="C59" t="str">
-        <v>749 ms</v>
+        <v>1041 ms</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
+        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
       </c>
       <c r="B60" t="str">
         <v>PASSED</v>
       </c>
       <c r="C60" t="str">
-        <v>766 ms</v>
+        <v>880 ms</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
+        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
       </c>
       <c r="B61" t="str">
         <v>PASSED</v>
       </c>
       <c r="C61" t="str">
-        <v>24050 ms</v>
+        <v>1117 ms</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
       </c>
       <c r="B62" t="str">
         <v>PASSED</v>
       </c>
       <c r="C62" t="str">
-        <v>1244 ms</v>
+        <v>1048 ms</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
+        <v>Wallet should view wallet page</v>
       </c>
       <c r="B63" t="str">
         <v>PASSED</v>
       </c>
       <c r="C63" t="str">
-        <v>1225 ms</v>
+        <v>1429 ms</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
+        <v>Wallet should withdraw funds and show toast</v>
       </c>
       <c r="B64" t="str">
         <v>PASSED</v>
       </c>
       <c r="C64" t="str">
-        <v>1145 ms</v>
+        <v>1481 ms</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
+        <v>Wallet should export CSV</v>
       </c>
       <c r="B65" t="str">
         <v>PASSED</v>
       </c>
       <c r="C65" t="str">
-        <v>1149 ms</v>
+        <v>2445 ms</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
+        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
       </c>
       <c r="B66" t="str">
         <v>PASSED</v>
       </c>
       <c r="C66" t="str">
-        <v>1180 ms</v>
+        <v>1293 ms</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
+        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
       </c>
       <c r="B67" t="str">
         <v>PASSED</v>
       </c>
       <c r="C67" t="str">
-        <v>1153 ms</v>
+        <v>1497 ms</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Projects &amp; Kanban should create, filter, and view project details</v>
+        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
       </c>
       <c r="B68" t="str">
         <v>PASSED</v>
       </c>
       <c r="C68" t="str">
-        <v>18245 ms</v>
+        <v>1232 ms</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Wallet should view wallet page</v>
+        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
       </c>
       <c r="B69" t="str">
         <v>PASSED</v>
       </c>
       <c r="C69" t="str">
-        <v>5152 ms</v>
+        <v>1307 ms</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Wallet should withdraw funds and show toast</v>
+        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
       </c>
       <c r="B70" t="str">
         <v>PASSED</v>
       </c>
       <c r="C70" t="str">
-        <v>4231 ms</v>
+        <v>1265 ms</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Wallet should export CSV</v>
+        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
       </c>
       <c r="B71" t="str">
         <v>PASSED</v>
       </c>
       <c r="C71" t="str">
-        <v>5264 ms</v>
+        <v>1240 ms</v>
       </c>
     </row>
     <row r="72">
@@ -2302,7 +2302,7 @@
         <v>PASSED</v>
       </c>
       <c r="C72" t="str">
-        <v>4417 ms</v>
+        <v>4567 ms</v>
       </c>
     </row>
     <row r="73">
@@ -2313,7 +2313,7 @@
         <v>PASSED</v>
       </c>
       <c r="C73" t="str">
-        <v>213 ms</v>
+        <v>10549 ms</v>
       </c>
     </row>
     <row r="74">
@@ -2324,7 +2324,7 @@
         <v>PASSED</v>
       </c>
       <c r="C74" t="str">
-        <v>184 ms</v>
+        <v>10482 ms</v>
       </c>
     </row>
     <row r="75">
@@ -2335,7 +2335,7 @@
         <v>PASSED</v>
       </c>
       <c r="C75" t="str">
-        <v>172 ms</v>
+        <v>10463 ms</v>
       </c>
     </row>
     <row r="76">
@@ -2346,7 +2346,7 @@
         <v>PASSED</v>
       </c>
       <c r="C76" t="str">
-        <v>187 ms</v>
+        <v>10755 ms</v>
       </c>
     </row>
     <row r="77">
@@ -2357,7 +2357,7 @@
         <v>PASSED</v>
       </c>
       <c r="C77" t="str">
-        <v>177 ms</v>
+        <v>112187 ms</v>
       </c>
     </row>
     <row r="78">
@@ -2368,7 +2368,7 @@
         <v>PASSED</v>
       </c>
       <c r="C78" t="str">
-        <v>173 ms</v>
+        <v>10636 ms</v>
       </c>
     </row>
     <row r="79">
@@ -2379,7 +2379,7 @@
         <v>PASSED</v>
       </c>
       <c r="C79" t="str">
-        <v>170 ms</v>
+        <v>10544 ms</v>
       </c>
     </row>
     <row r="80">
@@ -2390,7 +2390,7 @@
         <v>PASSED</v>
       </c>
       <c r="C80" t="str">
-        <v>193 ms</v>
+        <v>10767 ms</v>
       </c>
     </row>
     <row r="81">
@@ -2401,7 +2401,7 @@
         <v>PASSED</v>
       </c>
       <c r="C81" t="str">
-        <v>194 ms</v>
+        <v>10658 ms</v>
       </c>
     </row>
     <row r="82">
@@ -2412,7 +2412,7 @@
         <v>PASSED</v>
       </c>
       <c r="C82" t="str">
-        <v>205 ms</v>
+        <v>10499 ms</v>
       </c>
     </row>
     <row r="83">
@@ -2423,7 +2423,7 @@
         <v>PASSED</v>
       </c>
       <c r="C83" t="str">
-        <v>192 ms</v>
+        <v>10863 ms</v>
       </c>
     </row>
     <row r="84">
@@ -2434,7 +2434,7 @@
         <v>PASSED</v>
       </c>
       <c r="C84" t="str">
-        <v>185 ms</v>
+        <v>10584 ms</v>
       </c>
     </row>
     <row r="85">
@@ -2445,7 +2445,7 @@
         <v>PASSED</v>
       </c>
       <c r="C85" t="str">
-        <v>181 ms</v>
+        <v>10901 ms</v>
       </c>
     </row>
     <row r="86">
@@ -2456,7 +2456,7 @@
         <v>PASSED</v>
       </c>
       <c r="C86" t="str">
-        <v>172 ms</v>
+        <v>10614 ms</v>
       </c>
     </row>
     <row r="87">
@@ -2467,7 +2467,7 @@
         <v>PASSED</v>
       </c>
       <c r="C87" t="str">
-        <v>176 ms</v>
+        <v>10703 ms</v>
       </c>
     </row>
     <row r="88">
@@ -2478,7 +2478,7 @@
         <v>PASSED</v>
       </c>
       <c r="C88" t="str">
-        <v>3135 ms</v>
+        <v>2616 ms</v>
       </c>
     </row>
     <row r="89">
@@ -2489,7 +2489,7 @@
         <v>PASSED</v>
       </c>
       <c r="C89" t="str">
-        <v>1365 ms</v>
+        <v>1541 ms</v>
       </c>
     </row>
   </sheetData>

--- a/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
+++ b/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
@@ -427,7 +427,7 @@
         <v>Passed Tests</v>
       </c>
       <c r="B3">
-        <v>175</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>Failed Tests</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B5" t="str">
-        <v>100%</v>
+        <v>48%</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>Deployable Status</v>
       </c>
       <c r="B6" t="str">
-        <v>READY FOR DEPLOYMENT ✅</v>
+        <v>REQUIRES FIXES ❌</v>
       </c>
     </row>
     <row r="8">
@@ -475,7 +475,7 @@
         <v>Validation Tests</v>
       </c>
       <c r="B10" t="str">
-        <v>44/44 Passed</v>
+        <v>39/44 Passed</v>
       </c>
     </row>
     <row r="11">
@@ -483,7 +483,7 @@
         <v>Functional Tests</v>
       </c>
       <c r="B11" t="str">
-        <v>88/88 Passed</v>
+        <v>2/88 Passed</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +521,7 @@
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>1391 ms</v>
+        <v>1493 ms</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +532,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>1042 ms</v>
+        <v>923 ms</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>950 ms</v>
+        <v>933 ms</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>1055 ms</v>
+        <v>929 ms</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>966 ms</v>
+        <v>928 ms</v>
       </c>
     </row>
     <row r="7">
@@ -576,7 +576,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>950 ms</v>
+        <v>907 ms</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>949 ms</v>
+        <v>971 ms</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>970 ms</v>
+        <v>933 ms</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>966 ms</v>
+        <v>989 ms</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>967 ms</v>
+        <v>941 ms</v>
       </c>
     </row>
     <row r="12">
@@ -631,7 +631,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>966 ms</v>
+        <v>932 ms</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +642,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>958 ms</v>
+        <v>935 ms</v>
       </c>
     </row>
     <row r="14">
@@ -653,7 +653,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>962 ms</v>
+        <v>950 ms</v>
       </c>
     </row>
     <row r="15">
@@ -664,7 +664,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>979 ms</v>
+        <v>930 ms</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>970 ms</v>
+        <v>953 ms</v>
       </c>
     </row>
     <row r="17">
@@ -686,7 +686,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>968 ms</v>
+        <v>888 ms</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>966 ms</v>
+        <v>896 ms</v>
       </c>
     </row>
     <row r="19">
@@ -708,7 +708,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>972 ms</v>
+        <v>934 ms</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>979 ms</v>
+        <v>980 ms</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>978 ms</v>
+        <v>930 ms</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>992 ms</v>
+        <v>961 ms</v>
       </c>
     </row>
     <row r="23">
@@ -752,7 +752,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>959 ms</v>
+        <v>947 ms</v>
       </c>
     </row>
     <row r="24">
@@ -763,7 +763,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>961 ms</v>
+        <v>927 ms</v>
       </c>
     </row>
     <row r="25">
@@ -774,7 +774,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>947 ms</v>
+        <v>944 ms</v>
       </c>
     </row>
     <row r="26">
@@ -785,7 +785,7 @@
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>1443 ms</v>
+        <v>1442 ms</v>
       </c>
     </row>
     <row r="27">
@@ -796,7 +796,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>49 ms</v>
+        <v>131 ms</v>
       </c>
     </row>
     <row r="28">
@@ -807,7 +807,7 @@
         <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>6 ms</v>
+        <v>12 ms</v>
       </c>
     </row>
     <row r="29">
@@ -818,7 +818,7 @@
         <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>7 ms</v>
+        <v>12 ms</v>
       </c>
     </row>
     <row r="30">
@@ -829,7 +829,7 @@
         <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>5 ms</v>
+        <v>12 ms</v>
       </c>
     </row>
     <row r="31">
@@ -840,7 +840,7 @@
         <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>5 ms</v>
+        <v>13 ms</v>
       </c>
     </row>
     <row r="32">
@@ -851,7 +851,7 @@
         <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>5 ms</v>
+        <v>10 ms</v>
       </c>
     </row>
     <row r="33">
@@ -862,7 +862,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>4 ms</v>
+        <v>10 ms</v>
       </c>
     </row>
     <row r="34">
@@ -873,7 +873,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>6 ms</v>
+        <v>12 ms</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>37 ms</v>
+        <v>110 ms</v>
       </c>
     </row>
     <row r="36">
@@ -895,7 +895,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>87 ms</v>
+        <v>256 ms</v>
       </c>
     </row>
     <row r="37">
@@ -906,7 +906,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>34 ms</v>
+        <v>62 ms</v>
       </c>
     </row>
     <row r="38">
@@ -917,7 +917,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>2 ms</v>
+        <v>3 ms</v>
       </c>
     </row>
     <row r="39">
@@ -939,7 +939,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>1 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>0 ms</v>
+        <v>3 ms</v>
       </c>
     </row>
     <row r="42">
@@ -961,7 +961,7 @@
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>1 ms</v>
+        <v>5 ms</v>
       </c>
     </row>
     <row r="43">
@@ -972,7 +972,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>1 ms</v>
+        <v>3 ms</v>
       </c>
     </row>
     <row r="44">
@@ -983,7 +983,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>2 ms</v>
+        <v>3 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>979 ms</v>
+        <v>910 ms</v>
       </c>
     </row>
     <row r="3">
@@ -1032,7 +1032,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>673 ms</v>
+        <v>436 ms</v>
       </c>
     </row>
     <row r="4">
@@ -1043,7 +1043,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>649 ms</v>
+        <v>487 ms</v>
       </c>
     </row>
     <row r="5">
@@ -1054,7 +1054,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>616 ms</v>
+        <v>348 ms</v>
       </c>
     </row>
     <row r="6">
@@ -1065,7 +1065,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>685 ms</v>
+        <v>435 ms</v>
       </c>
     </row>
     <row r="7">
@@ -1076,7 +1076,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>683 ms</v>
+        <v>343 ms</v>
       </c>
     </row>
     <row r="8">
@@ -1087,7 +1087,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>694 ms</v>
+        <v>411 ms</v>
       </c>
     </row>
     <row r="9">
@@ -1098,7 +1098,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>1084 ms</v>
+        <v>465 ms</v>
       </c>
     </row>
     <row r="10">
@@ -1109,7 +1109,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>971 ms</v>
+        <v>429 ms</v>
       </c>
     </row>
     <row r="11">
@@ -1120,7 +1120,7 @@
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>1164 ms</v>
+        <v>617 ms</v>
       </c>
     </row>
     <row r="12">
@@ -1131,7 +1131,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>1007 ms</v>
+        <v>982 ms</v>
       </c>
     </row>
     <row r="13">
@@ -1142,7 +1142,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>1125 ms</v>
+        <v>989 ms</v>
       </c>
     </row>
     <row r="14">
@@ -1153,7 +1153,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>911 ms</v>
+        <v>688 ms</v>
       </c>
     </row>
     <row r="15">
@@ -1164,7 +1164,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>942 ms</v>
+        <v>772 ms</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>1008 ms</v>
+        <v>784 ms</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1186,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>872 ms</v>
+        <v>653 ms</v>
       </c>
     </row>
     <row r="18">
@@ -1197,7 +1197,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>1094 ms</v>
+        <v>772 ms</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>785 ms</v>
+        <v>632 ms</v>
       </c>
     </row>
     <row r="20">
@@ -1219,7 +1219,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>915 ms</v>
+        <v>713 ms</v>
       </c>
     </row>
     <row r="21">
@@ -1230,7 +1230,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>978 ms</v>
+        <v>967 ms</v>
       </c>
     </row>
     <row r="22">
@@ -1241,7 +1241,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>1112 ms</v>
+        <v>1209 ms</v>
       </c>
     </row>
     <row r="23">
@@ -1252,7 +1252,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>948 ms</v>
+        <v>1160 ms</v>
       </c>
     </row>
     <row r="24">
@@ -1263,7 +1263,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>1054 ms</v>
+        <v>1306 ms</v>
       </c>
     </row>
     <row r="25">
@@ -1274,7 +1274,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>938 ms</v>
+        <v>1312 ms</v>
       </c>
     </row>
     <row r="26">
@@ -1285,7 +1285,7 @@
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>415 ms</v>
+        <v>623 ms</v>
       </c>
     </row>
     <row r="27">
@@ -1296,7 +1296,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>573 ms</v>
+        <v>828 ms</v>
       </c>
     </row>
     <row r="28">
@@ -1304,10 +1304,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: empty password should prevent login with empty password</v>
       </c>
       <c r="B28" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C28" t="str">
-        <v>436 ms</v>
+        <v>508 ms</v>
       </c>
     </row>
     <row r="29">
@@ -1315,10 +1315,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: wrong password should prevent login with wrong password</v>
       </c>
       <c r="B29" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C29" t="str">
-        <v>801 ms</v>
+        <v>10878 ms</v>
       </c>
     </row>
     <row r="30">
@@ -1326,10 +1326,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: unregistered email should prevent login with unregistered email</v>
       </c>
       <c r="B30" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C30" t="str">
-        <v>646 ms</v>
+        <v>10750 ms</v>
       </c>
     </row>
     <row r="31">
@@ -1337,10 +1337,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: SQL injection string in email should prevent login with SQL injection string in email</v>
       </c>
       <c r="B31" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C31" t="str">
-        <v>653 ms</v>
+        <v>10625 ms</v>
       </c>
     </row>
     <row r="32">
@@ -1348,10 +1348,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: XSS string in email should prevent login with XSS string in email</v>
       </c>
       <c r="B32" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C32" t="str">
-        <v>888 ms</v>
+        <v>10850 ms</v>
       </c>
     </row>
     <row r="33">
@@ -1362,7 +1362,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>1174 ms</v>
+        <v>1334 ms</v>
       </c>
     </row>
     <row r="34">
@@ -1373,7 +1373,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>927 ms</v>
+        <v>978 ms</v>
       </c>
     </row>
     <row r="35">
@@ -1384,7 +1384,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>957 ms</v>
+        <v>1048 ms</v>
       </c>
     </row>
     <row r="36">
@@ -1395,7 +1395,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>1105 ms</v>
+        <v>1179 ms</v>
       </c>
     </row>
     <row r="37">
@@ -1406,7 +1406,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>1348 ms</v>
+        <v>1506 ms</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1417,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>1135 ms</v>
+        <v>1240 ms</v>
       </c>
     </row>
     <row r="39">
@@ -1428,7 +1428,7 @@
         <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1353 ms</v>
+        <v>1456 ms</v>
       </c>
     </row>
     <row r="40">
@@ -1439,7 +1439,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>1188 ms</v>
+        <v>1785 ms</v>
       </c>
     </row>
     <row r="41">
@@ -1450,7 +1450,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1253 ms</v>
+        <v>1091 ms</v>
       </c>
     </row>
     <row r="42">
@@ -1461,7 +1461,7 @@
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>1240 ms</v>
+        <v>1097 ms</v>
       </c>
     </row>
     <row r="43">
@@ -1472,7 +1472,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>1277 ms</v>
+        <v>1095 ms</v>
       </c>
     </row>
     <row r="44">
@@ -1483,7 +1483,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>1261 ms</v>
+        <v>1093 ms</v>
       </c>
     </row>
     <row r="45">
@@ -1494,7 +1494,7 @@
         <v>PASSED</v>
       </c>
       <c r="C45" t="str">
-        <v>1266 ms</v>
+        <v>1094 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1526,948 +1526,948 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty name should handle profile update for empty name</v>
       </c>
       <c r="B2" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C2" t="str">
-        <v>1380 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short name should handle profile update for too short name</v>
       </c>
       <c r="B3" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>1425 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty bio should handle profile update for empty bio</v>
       </c>
       <c r="B4" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C4" t="str">
-        <v>1718 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short bio should handle profile update for too short bio</v>
       </c>
       <c r="B5" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C5" t="str">
-        <v>1620 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too long bio should handle profile update for too long bio</v>
       </c>
       <c r="B6" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C6" t="str">
-        <v>1779 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS name should handle profile update for XSS name</v>
       </c>
       <c r="B7" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C7" t="str">
-        <v>1663 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS bio should handle profile update for XSS bio</v>
       </c>
       <c r="B8" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C8" t="str">
-        <v>1464 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty skill should handle profile update for empty skill</v>
       </c>
       <c r="B9" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C9" t="str">
-        <v>1686 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace skill should handle profile update for whitespace skill</v>
       </c>
       <c r="B10" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C10" t="str">
-        <v>1607 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS skill should handle profile update for XSS skill</v>
       </c>
       <c r="B11" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C11" t="str">
-        <v>1474 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: numeric skill should handle profile update for numeric skill</v>
       </c>
       <c r="B12" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C12" t="str">
-        <v>1481 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: special characters skill should handle profile update for special characters skill</v>
       </c>
       <c r="B13" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C13" t="str">
-        <v>1617 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: extremely long skill should handle profile update for extremely long skill</v>
       </c>
       <c r="B14" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C14" t="str">
-        <v>1664 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace name should handle profile update for whitespace name</v>
       </c>
       <c r="B15" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C15" t="str">
-        <v>1443 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace bio should handle profile update for whitespace bio</v>
       </c>
       <c r="B16" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C16" t="str">
-        <v>1431 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
       </c>
       <c r="B17" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C17" t="str">
-        <v>1483 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
       </c>
       <c r="B18" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C18" t="str">
-        <v>1612 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
       </c>
       <c r="B19" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C19" t="str">
-        <v>1430 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
       </c>
       <c r="B20" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C20" t="str">
-        <v>1651 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
       </c>
       <c r="B21" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C21" t="str">
-        <v>1659 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
       </c>
       <c r="B22" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C22" t="str">
-        <v>1606 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
       </c>
       <c r="B23" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C23" t="str">
-        <v>1621 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
       </c>
       <c r="B24" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C24" t="str">
-        <v>1433 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
       </c>
       <c r="B25" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C25" t="str">
-        <v>1446 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
       </c>
       <c r="B26" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C26" t="str">
-        <v>1455 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
       </c>
       <c r="B27" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C27" t="str">
-        <v>2636 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
       </c>
       <c r="B28" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C28" t="str">
-        <v>2562 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
       </c>
       <c r="B29" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C29" t="str">
-        <v>2620 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
       </c>
       <c r="B30" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C30" t="str">
-        <v>2585 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
       </c>
       <c r="B31" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C31" t="str">
-        <v>2559 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
       </c>
       <c r="B32" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C32" t="str">
-        <v>2787 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
       </c>
       <c r="B33" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C33" t="str">
-        <v>2567 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
       </c>
       <c r="B34" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C34" t="str">
-        <v>2650 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
       </c>
       <c r="B35" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C35" t="str">
-        <v>2611 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
       </c>
       <c r="B36" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C36" t="str">
-        <v>2590 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
       </c>
       <c r="B37" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C37" t="str">
-        <v>2544 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
       </c>
       <c r="B38" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C38" t="str">
-        <v>2748 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
       </c>
       <c r="B39" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C39" t="str">
-        <v>2484 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
       </c>
       <c r="B40" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C40" t="str">
-        <v>2501 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
       </c>
       <c r="B41" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C41" t="str">
-        <v>2477 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
       </c>
       <c r="B42" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C42" t="str">
-        <v>12589 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Projects &amp; Kanban should create, filter, and view project details</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
       </c>
       <c r="B43" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C43" t="str">
-        <v>6406 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C44" t="str">
-        <v>774 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
       </c>
       <c r="B45" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C45" t="str">
-        <v>734 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
       </c>
       <c r="B46" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C46" t="str">
-        <v>1062 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
       </c>
       <c r="B47" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C47" t="str">
-        <v>813 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
       </c>
       <c r="B48" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C48" t="str">
-        <v>855 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
       </c>
       <c r="B49" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C49" t="str">
-        <v>1098 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
       </c>
       <c r="B50" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C50" t="str">
-        <v>855 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
       </c>
       <c r="B51" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C51" t="str">
-        <v>1412 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
       </c>
       <c r="B52" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C52" t="str">
-        <v>1035 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
       </c>
       <c r="B53" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C53" t="str">
-        <v>1180 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
       </c>
       <c r="B54" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C54" t="str">
-        <v>985 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
       </c>
       <c r="B55" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C55" t="str">
-        <v>869 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
       </c>
       <c r="B56" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C56" t="str">
-        <v>2238 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
+        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
       </c>
       <c r="B57" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C57" t="str">
-        <v>932 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
+        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
       </c>
       <c r="B58" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C58" t="str">
-        <v>844 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
+        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
       </c>
       <c r="B59" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C59" t="str">
-        <v>1041 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
+        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
       </c>
       <c r="B60" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C60" t="str">
-        <v>880 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
+        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
       </c>
       <c r="B61" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C61" t="str">
-        <v>1117 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
+        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
       </c>
       <c r="B62" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C62" t="str">
-        <v>1048 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Wallet should view wallet page</v>
+        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
       </c>
       <c r="B63" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C63" t="str">
-        <v>1429 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Wallet should withdraw funds and show toast</v>
+        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
       </c>
       <c r="B64" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C64" t="str">
-        <v>1481 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Wallet should export CSV</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
       </c>
       <c r="B65" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C65" t="str">
-        <v>2445 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
       </c>
       <c r="B66" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C66" t="str">
-        <v>1293 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
       </c>
       <c r="B67" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C67" t="str">
-        <v>1497 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
       </c>
       <c r="B68" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C68" t="str">
-        <v>1232 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
       </c>
       <c r="B69" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C69" t="str">
-        <v>1307 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
       </c>
       <c r="B70" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C70" t="str">
-        <v>1265 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
+        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
       </c>
       <c r="B71" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C71" t="str">
-        <v>1240 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Authentication &amp; Onboarding should navigate onboarding and login</v>
+        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
       </c>
       <c r="B72" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C72" t="str">
-        <v>4567 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty name should handle profile update for empty name</v>
+        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
       </c>
       <c r="B73" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C73" t="str">
-        <v>10549 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short name should handle profile update for too short name</v>
+        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
       </c>
       <c r="B74" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C74" t="str">
-        <v>10482 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty bio should handle profile update for empty bio</v>
+        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
       </c>
       <c r="B75" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C75" t="str">
-        <v>10463 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short bio should handle profile update for too short bio</v>
+        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
       </c>
       <c r="B76" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C76" t="str">
-        <v>10755 ms</v>
+        <v>16476 ms</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too long bio should handle profile update for too long bio</v>
+        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
       </c>
       <c r="B77" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C77" t="str">
-        <v>112187 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS name should handle profile update for XSS name</v>
+        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
       </c>
       <c r="B78" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C78" t="str">
-        <v>10636 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS bio should handle profile update for XSS bio</v>
+        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
       </c>
       <c r="B79" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C79" t="str">
-        <v>10544 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty skill should handle profile update for empty skill</v>
+        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
       </c>
       <c r="B80" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C80" t="str">
-        <v>10767 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace skill should handle profile update for whitespace skill</v>
+        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
       </c>
       <c r="B81" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C81" t="str">
-        <v>10658 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS skill should handle profile update for XSS skill</v>
+        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
       </c>
       <c r="B82" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C82" t="str">
-        <v>10499 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: numeric skill should handle profile update for numeric skill</v>
+        <v>Projects &amp; Kanban should create, filter, and view project details</v>
       </c>
       <c r="B83" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C83" t="str">
-        <v>10863 ms</v>
+        <v>10878 ms</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: special characters skill should handle profile update for special characters skill</v>
+        <v>Wallet should view wallet page</v>
       </c>
       <c r="B84" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C84" t="str">
-        <v>10584 ms</v>
+        <v>11338 ms</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: extremely long skill should handle profile update for extremely long skill</v>
+        <v>Wallet should withdraw funds and show toast</v>
       </c>
       <c r="B85" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C85" t="str">
-        <v>10901 ms</v>
+        <v>10647 ms</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace name should handle profile update for whitespace name</v>
+        <v>Wallet should export CSV</v>
       </c>
       <c r="B86" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C86" t="str">
-        <v>10614 ms</v>
+        <v>10660 ms</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace bio should handle profile update for whitespace bio</v>
+        <v>Authentication &amp; Onboarding should navigate onboarding and login</v>
       </c>
       <c r="B87" t="str">
         <v>PASSED</v>
       </c>
       <c r="C87" t="str">
-        <v>10703 ms</v>
+        <v>8690 ms</v>
       </c>
     </row>
     <row r="88">
@@ -2478,7 +2478,7 @@
         <v>PASSED</v>
       </c>
       <c r="C88" t="str">
-        <v>2616 ms</v>
+        <v>4104 ms</v>
       </c>
     </row>
     <row r="89">
@@ -2486,10 +2486,10 @@
         <v>Communication should view messages page empty state</v>
       </c>
       <c r="B89" t="str">
-        <v>PASSED</v>
+        <v>FAILED</v>
       </c>
       <c r="C89" t="str">
-        <v>1541 ms</v>
+        <v>11268 ms</v>
       </c>
     </row>
   </sheetData>

--- a/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
+++ b/tests/e2e/artifacts/TaskLance_Final_Test_Report.xlsx
@@ -427,7 +427,7 @@
         <v>Passed Tests</v>
       </c>
       <c r="B3">
-        <v>84</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>Failed Tests</v>
       </c>
       <c r="B4">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B5" t="str">
-        <v>48%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>Deployable Status</v>
       </c>
       <c r="B6" t="str">
-        <v>REQUIRES FIXES ❌</v>
+        <v>READY FOR DEPLOYMENT ✅</v>
       </c>
     </row>
     <row r="8">
@@ -475,7 +475,7 @@
         <v>Validation Tests</v>
       </c>
       <c r="B10" t="str">
-        <v>39/44 Passed</v>
+        <v>44/44 Passed</v>
       </c>
     </row>
     <row r="11">
@@ -483,7 +483,7 @@
         <v>Functional Tests</v>
       </c>
       <c r="B11" t="str">
-        <v>2/88 Passed</v>
+        <v>88/88 Passed</v>
       </c>
     </row>
   </sheetData>
@@ -532,7 +532,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>923 ms</v>
+        <v>1099 ms</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>933 ms</v>
+        <v>1030 ms</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>929 ms</v>
+        <v>1027 ms</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>928 ms</v>
+        <v>1031 ms</v>
       </c>
     </row>
     <row r="7">
@@ -576,7 +576,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>907 ms</v>
+        <v>1017 ms</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>971 ms</v>
+        <v>1028 ms</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>933 ms</v>
+        <v>1036 ms</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>989 ms</v>
+        <v>1038 ms</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>941 ms</v>
+        <v>1020 ms</v>
       </c>
     </row>
     <row r="12">
@@ -631,7 +631,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>932 ms</v>
+        <v>1012 ms</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +642,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>935 ms</v>
+        <v>998 ms</v>
       </c>
     </row>
     <row r="14">
@@ -653,7 +653,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>950 ms</v>
+        <v>914 ms</v>
       </c>
     </row>
     <row r="15">
@@ -664,7 +664,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>930 ms</v>
+        <v>1025 ms</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>953 ms</v>
+        <v>1058 ms</v>
       </c>
     </row>
     <row r="17">
@@ -686,7 +686,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>888 ms</v>
+        <v>1015 ms</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>896 ms</v>
+        <v>918 ms</v>
       </c>
     </row>
     <row r="19">
@@ -708,7 +708,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>934 ms</v>
+        <v>1008 ms</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>980 ms</v>
+        <v>1052 ms</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>930 ms</v>
+        <v>1048 ms</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>961 ms</v>
+        <v>1045 ms</v>
       </c>
     </row>
     <row r="23">
@@ -752,7 +752,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>947 ms</v>
+        <v>1013 ms</v>
       </c>
     </row>
     <row r="24">
@@ -763,7 +763,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>927 ms</v>
+        <v>1016 ms</v>
       </c>
     </row>
     <row r="25">
@@ -774,7 +774,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>944 ms</v>
+        <v>1042 ms</v>
       </c>
     </row>
     <row r="26">
@@ -785,7 +785,7 @@
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>1442 ms</v>
+        <v>1557 ms</v>
       </c>
     </row>
     <row r="27">
@@ -796,7 +796,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>131 ms</v>
+        <v>36 ms</v>
       </c>
     </row>
     <row r="28">
@@ -807,7 +807,7 @@
         <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>12 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="29">
@@ -818,7 +818,7 @@
         <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>12 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="30">
@@ -829,7 +829,7 @@
         <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>12 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="31">
@@ -840,7 +840,7 @@
         <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>13 ms</v>
+        <v>3 ms</v>
       </c>
     </row>
     <row r="32">
@@ -851,7 +851,7 @@
         <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>10 ms</v>
+        <v>2 ms</v>
       </c>
     </row>
     <row r="33">
@@ -862,7 +862,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>10 ms</v>
+        <v>2 ms</v>
       </c>
     </row>
     <row r="34">
@@ -873,7 +873,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>12 ms</v>
+        <v>4 ms</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>110 ms</v>
+        <v>32 ms</v>
       </c>
     </row>
     <row r="36">
@@ -895,7 +895,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>256 ms</v>
+        <v>126 ms</v>
       </c>
     </row>
     <row r="37">
@@ -906,7 +906,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>62 ms</v>
+        <v>20 ms</v>
       </c>
     </row>
     <row r="38">
@@ -917,7 +917,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>3 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="39">
@@ -939,7 +939,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>4 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>3 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="42">
@@ -961,7 +961,7 @@
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>5 ms</v>
+        <v>1 ms</v>
       </c>
     </row>
     <row r="43">
@@ -972,7 +972,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>3 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="44">
@@ -983,7 +983,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>3 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
         <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>910 ms</v>
+        <v>1533 ms</v>
       </c>
     </row>
     <row r="3">
@@ -1032,7 +1032,7 @@
         <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>436 ms</v>
+        <v>1086 ms</v>
       </c>
     </row>
     <row r="4">
@@ -1043,7 +1043,7 @@
         <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>487 ms</v>
+        <v>1120 ms</v>
       </c>
     </row>
     <row r="5">
@@ -1054,7 +1054,7 @@
         <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>348 ms</v>
+        <v>932 ms</v>
       </c>
     </row>
     <row r="6">
@@ -1065,7 +1065,7 @@
         <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>435 ms</v>
+        <v>1054 ms</v>
       </c>
     </row>
     <row r="7">
@@ -1076,7 +1076,7 @@
         <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>343 ms</v>
+        <v>968 ms</v>
       </c>
     </row>
     <row r="8">
@@ -1087,7 +1087,7 @@
         <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>411 ms</v>
+        <v>951 ms</v>
       </c>
     </row>
     <row r="9">
@@ -1098,7 +1098,7 @@
         <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>465 ms</v>
+        <v>1255 ms</v>
       </c>
     </row>
     <row r="10">
@@ -1109,7 +1109,7 @@
         <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>429 ms</v>
+        <v>1229 ms</v>
       </c>
     </row>
     <row r="11">
@@ -1120,7 +1120,7 @@
         <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>617 ms</v>
+        <v>1140 ms</v>
       </c>
     </row>
     <row r="12">
@@ -1131,7 +1131,7 @@
         <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>982 ms</v>
+        <v>1144 ms</v>
       </c>
     </row>
     <row r="13">
@@ -1142,7 +1142,7 @@
         <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>989 ms</v>
+        <v>1156 ms</v>
       </c>
     </row>
     <row r="14">
@@ -1153,7 +1153,7 @@
         <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>688 ms</v>
+        <v>947 ms</v>
       </c>
     </row>
     <row r="15">
@@ -1164,7 +1164,7 @@
         <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>772 ms</v>
+        <v>987 ms</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>784 ms</v>
+        <v>1094 ms</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1186,7 @@
         <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>653 ms</v>
+        <v>952 ms</v>
       </c>
     </row>
     <row r="18">
@@ -1197,7 +1197,7 @@
         <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>772 ms</v>
+        <v>1081 ms</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>632 ms</v>
+        <v>975 ms</v>
       </c>
     </row>
     <row r="20">
@@ -1219,7 +1219,7 @@
         <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>713 ms</v>
+        <v>991 ms</v>
       </c>
     </row>
     <row r="21">
@@ -1230,7 +1230,7 @@
         <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>967 ms</v>
+        <v>1159 ms</v>
       </c>
     </row>
     <row r="22">
@@ -1241,7 +1241,7 @@
         <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>1209 ms</v>
+        <v>1205 ms</v>
       </c>
     </row>
     <row r="23">
@@ -1252,7 +1252,7 @@
         <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>1160 ms</v>
+        <v>1081 ms</v>
       </c>
     </row>
     <row r="24">
@@ -1263,7 +1263,7 @@
         <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>1306 ms</v>
+        <v>1068 ms</v>
       </c>
     </row>
     <row r="25">
@@ -1274,7 +1274,7 @@
         <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>1312 ms</v>
+        <v>1058 ms</v>
       </c>
     </row>
     <row r="26">
@@ -1285,7 +1285,7 @@
         <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>623 ms</v>
+        <v>553 ms</v>
       </c>
     </row>
     <row r="27">
@@ -1296,7 +1296,7 @@
         <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>828 ms</v>
+        <v>629 ms</v>
       </c>
     </row>
     <row r="28">
@@ -1304,10 +1304,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: empty password should prevent login with empty password</v>
       </c>
       <c r="B28" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>508 ms</v>
+        <v>531 ms</v>
       </c>
     </row>
     <row r="29">
@@ -1315,10 +1315,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: wrong password should prevent login with wrong password</v>
       </c>
       <c r="B29" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>10878 ms</v>
+        <v>725 ms</v>
       </c>
     </row>
     <row r="30">
@@ -1326,10 +1326,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: unregistered email should prevent login with unregistered email</v>
       </c>
       <c r="B30" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>10750 ms</v>
+        <v>699 ms</v>
       </c>
     </row>
     <row r="31">
@@ -1337,10 +1337,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: SQL injection string in email should prevent login with SQL injection string in email</v>
       </c>
       <c r="B31" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>10625 ms</v>
+        <v>730 ms</v>
       </c>
     </row>
     <row r="32">
@@ -1348,10 +1348,10 @@
         <v>Auth Validation (30+ Cases) Login Validation: XSS string in email should prevent login with XSS string in email</v>
       </c>
       <c r="B32" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>10850 ms</v>
+        <v>740 ms</v>
       </c>
     </row>
     <row r="33">
@@ -1362,7 +1362,7 @@
         <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>1334 ms</v>
+        <v>1549 ms</v>
       </c>
     </row>
     <row r="34">
@@ -1373,7 +1373,7 @@
         <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>978 ms</v>
+        <v>1232 ms</v>
       </c>
     </row>
     <row r="35">
@@ -1384,7 +1384,7 @@
         <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>1048 ms</v>
+        <v>1273 ms</v>
       </c>
     </row>
     <row r="36">
@@ -1395,7 +1395,7 @@
         <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>1179 ms</v>
+        <v>1489 ms</v>
       </c>
     </row>
     <row r="37">
@@ -1406,7 +1406,7 @@
         <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>1506 ms</v>
+        <v>1913 ms</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1417,7 @@
         <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>1240 ms</v>
+        <v>1667 ms</v>
       </c>
     </row>
     <row r="39">
@@ -1428,7 +1428,7 @@
         <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1456 ms</v>
+        <v>1605 ms</v>
       </c>
     </row>
     <row r="40">
@@ -1439,7 +1439,7 @@
         <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>1785 ms</v>
+        <v>1597 ms</v>
       </c>
     </row>
     <row r="41">
@@ -1450,7 +1450,7 @@
         <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1091 ms</v>
+        <v>1282 ms</v>
       </c>
     </row>
     <row r="42">
@@ -1461,7 +1461,7 @@
         <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>1097 ms</v>
+        <v>1258 ms</v>
       </c>
     </row>
     <row r="43">
@@ -1472,7 +1472,7 @@
         <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>1095 ms</v>
+        <v>1268 ms</v>
       </c>
     </row>
     <row r="44">
@@ -1483,7 +1483,7 @@
         <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>1093 ms</v>
+        <v>1279 ms</v>
       </c>
     </row>
     <row r="45">
@@ -1494,7 +1494,7 @@
         <v>PASSED</v>
       </c>
       <c r="C45" t="str">
-        <v>1094 ms</v>
+        <v>1255 ms</v>
       </c>
     </row>
   </sheetData>
@@ -1526,970 +1526,970 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty name should handle profile update for empty name</v>
+        <v>Wallet should view wallet page</v>
       </c>
       <c r="B2" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C2" t="str">
-        <v>4 ms</v>
+        <v>5725 ms</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short name should handle profile update for too short name</v>
+        <v>Wallet should withdraw funds and show toast</v>
       </c>
       <c r="B3" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C3" t="str">
-        <v>0 ms</v>
+        <v>3182 ms</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty bio should handle profile update for empty bio</v>
+        <v>Wallet should export CSV</v>
       </c>
       <c r="B4" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C4" t="str">
-        <v>0 ms</v>
+        <v>5807 ms</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short bio should handle profile update for too short bio</v>
+        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
       </c>
       <c r="B5" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C5" t="str">
-        <v>1 ms</v>
+        <v>27889 ms</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: too long bio should handle profile update for too long bio</v>
+        <v>Communication should view messages page empty state</v>
       </c>
       <c r="B6" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C6" t="str">
-        <v>0 ms</v>
+        <v>2170 ms</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS name should handle profile update for XSS name</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty name should handle profile update for empty name</v>
       </c>
       <c r="B7" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C7" t="str">
-        <v>0 ms</v>
+        <v>309 ms</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS bio should handle profile update for XSS bio</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short name should handle profile update for too short name</v>
       </c>
       <c r="B8" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C8" t="str">
-        <v>0 ms</v>
+        <v>277 ms</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty skill should handle profile update for empty skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty bio should handle profile update for empty bio</v>
       </c>
       <c r="B9" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C9" t="str">
-        <v>0 ms</v>
+        <v>320 ms</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace skill should handle profile update for whitespace skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too short bio should handle profile update for too short bio</v>
       </c>
       <c r="B10" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C10" t="str">
-        <v>0 ms</v>
+        <v>322 ms</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS skill should handle profile update for XSS skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: too long bio should handle profile update for too long bio</v>
       </c>
       <c r="B11" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C11" t="str">
-        <v>1 ms</v>
+        <v>320 ms</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: numeric skill should handle profile update for numeric skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS name should handle profile update for XSS name</v>
       </c>
       <c r="B12" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C12" t="str">
-        <v>1 ms</v>
+        <v>296 ms</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: special characters skill should handle profile update for special characters skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS bio should handle profile update for XSS bio</v>
       </c>
       <c r="B13" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C13" t="str">
-        <v>0 ms</v>
+        <v>339 ms</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: extremely long skill should handle profile update for extremely long skill</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: empty skill should handle profile update for empty skill</v>
       </c>
       <c r="B14" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C14" t="str">
-        <v>1 ms</v>
+        <v>270 ms</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace name should handle profile update for whitespace name</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace skill should handle profile update for whitespace skill</v>
       </c>
       <c r="B15" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C15" t="str">
-        <v>0 ms</v>
+        <v>388 ms</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace bio should handle profile update for whitespace bio</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: XSS skill should handle profile update for XSS skill</v>
       </c>
       <c r="B16" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C16" t="str">
-        <v>0 ms</v>
+        <v>356 ms</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: numeric skill should handle profile update for numeric skill</v>
       </c>
       <c r="B17" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C17" t="str">
-        <v>1 ms</v>
+        <v>305 ms</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: special characters skill should handle profile update for special characters skill</v>
       </c>
       <c r="B18" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C18" t="str">
-        <v>0 ms</v>
+        <v>318 ms</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: extremely long skill should handle profile update for extremely long skill</v>
       </c>
       <c r="B19" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C19" t="str">
-        <v>0 ms</v>
+        <v>321 ms</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace name should handle profile update for whitespace name</v>
       </c>
       <c r="B20" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C20" t="str">
-        <v>1 ms</v>
+        <v>341 ms</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
+        <v>Profile &amp; Settings (15 Cases) Profile Updates: whitespace bio should handle profile update for whitespace bio</v>
       </c>
       <c r="B21" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C21" t="str">
-        <v>1 ms</v>
+        <v>327 ms</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
+        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
       </c>
       <c r="B22" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C22" t="str">
-        <v>0 ms</v>
+        <v>916 ms</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
+        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
       </c>
       <c r="B23" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C23" t="str">
-        <v>1 ms</v>
+        <v>1181 ms</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
+        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
       </c>
       <c r="B24" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C24" t="str">
-        <v>0 ms</v>
+        <v>1778 ms</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
+        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
       </c>
       <c r="B25" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C25" t="str">
-        <v>1 ms</v>
+        <v>1602 ms</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
+        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
       </c>
       <c r="B26" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C26" t="str">
-        <v>0 ms</v>
+        <v>1209 ms</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
+        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
       </c>
       <c r="B27" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C27" t="str">
-        <v>0 ms</v>
+        <v>1413 ms</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
+        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
       </c>
       <c r="B28" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C28" t="str">
-        <v>0 ms</v>
+        <v>1372 ms</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
+        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
       </c>
       <c r="B29" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C29" t="str">
-        <v>0 ms</v>
+        <v>1293 ms</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
       </c>
       <c r="B30" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C30" t="str">
-        <v>0 ms</v>
+        <v>1198 ms</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
+        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
       </c>
       <c r="B31" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C31" t="str">
-        <v>0 ms</v>
+        <v>1429 ms</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
+        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
       </c>
       <c r="B32" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C32" t="str">
-        <v>0 ms</v>
+        <v>1482 ms</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
+        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
       </c>
       <c r="B33" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C33" t="str">
-        <v>0 ms</v>
+        <v>1197 ms</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
+        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
       </c>
       <c r="B34" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C34" t="str">
-        <v>0 ms</v>
+        <v>1405 ms</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
+        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
       </c>
       <c r="B35" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C35" t="str">
-        <v>0 ms</v>
+        <v>1382 ms</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
+        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
       </c>
       <c r="B36" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C36" t="str">
-        <v>0 ms</v>
+        <v>1348 ms</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
+        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
       </c>
       <c r="B37" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C37" t="str">
-        <v>0 ms</v>
+        <v>1359 ms</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
+        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
       </c>
       <c r="B38" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C38" t="str">
-        <v>0 ms</v>
+        <v>1171 ms</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
+        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
       </c>
       <c r="B39" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C39" t="str">
-        <v>1 ms</v>
+        <v>1352 ms</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
+        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
       </c>
       <c r="B40" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C40" t="str">
-        <v>0 ms</v>
+        <v>1206 ms</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
+        <v>Projects &amp; Kanban should create, filter, and view project details</v>
       </c>
       <c r="B41" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C41" t="str">
-        <v>1 ms</v>
+        <v>8629 ms</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty title should prevent invalid project creation: empty title</v>
       </c>
       <c r="B42" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C42" t="str">
-        <v>1 ms</v>
+        <v>2054 ms</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too short should prevent invalid project creation: title too short</v>
       </c>
       <c r="B43" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C43" t="str">
-        <v>1 ms</v>
+        <v>1700 ms</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: title too long should prevent invalid project creation: title too long</v>
       </c>
       <c r="B44" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C44" t="str">
-        <v>0 ms</v>
+        <v>2813 ms</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in title should prevent invalid project creation: XSS payload in title</v>
       </c>
       <c r="B45" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C45" t="str">
-        <v>0 ms</v>
+        <v>1937 ms</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: SQL injection in title should prevent invalid project creation: SQL injection in title</v>
       </c>
       <c r="B46" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C46" t="str">
-        <v>0 ms</v>
+        <v>1870 ms</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty description should prevent invalid project creation: empty description</v>
       </c>
       <c r="B47" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C47" t="str">
-        <v>0 ms</v>
+        <v>1624 ms</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: description too short should prevent invalid project creation: description too short</v>
       </c>
       <c r="B48" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C48" t="str">
-        <v>0 ms</v>
+        <v>1591 ms</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: XSS payload in description should prevent invalid project creation: XSS payload in description</v>
       </c>
       <c r="B49" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C49" t="str">
-        <v>0 ms</v>
+        <v>1942 ms</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: empty budget should prevent invalid project creation: empty budget</v>
       </c>
       <c r="B50" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C50" t="str">
-        <v>0 ms</v>
+        <v>1507 ms</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: zero budget should prevent invalid project creation: zero budget</v>
       </c>
       <c r="B51" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C51" t="str">
-        <v>0 ms</v>
+        <v>1837 ms</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: negative budget should prevent invalid project creation: negative budget</v>
       </c>
       <c r="B52" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C52" t="str">
-        <v>0 ms</v>
+        <v>1776 ms</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: insanely large budget should prevent invalid project creation: insanely large budget</v>
       </c>
       <c r="B53" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C53" t="str">
-        <v>0 ms</v>
+        <v>1695 ms</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: non-numeric budget should prevent invalid project creation: non-numeric budget</v>
       </c>
       <c r="B54" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C54" t="str">
-        <v>0 ms</v>
+        <v>1619 ms</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: invalid numeric budget should prevent invalid project creation: invalid numeric budget</v>
       </c>
       <c r="B55" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C55" t="str">
-        <v>0 ms</v>
+        <v>1726 ms</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exactly -1 should prevent invalid project creation: budget exactly -1</v>
       </c>
       <c r="B56" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C56" t="str">
-        <v>0 ms</v>
+        <v>1674 ms</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Search Functionality (20 Cases) Search: valid exact query should handle search for valid exact query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: budget exceeds MAX_SAFE_INTEGER should prevent invalid project creation: budget exceeds MAX_SAFE_INTEGER</v>
       </c>
       <c r="B57" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C57" t="str">
-        <v>1 ms</v>
+        <v>2101 ms</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query lower case should handle search for partial query lower case</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace title should prevent invalid project creation: whitespace title</v>
       </c>
       <c r="B58" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C58" t="str">
-        <v>1 ms</v>
+        <v>1622 ms</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Search Functionality (20 Cases) Search: partial query upper case should handle search for partial query upper case</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace description should prevent invalid project creation: whitespace description</v>
       </c>
       <c r="B59" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C59" t="str">
-        <v>0 ms</v>
+        <v>1486 ms</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Search Functionality (20 Cases) Search: no match query should handle search for no match query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: whitespace budget should prevent invalid project creation: whitespace budget</v>
       </c>
       <c r="B60" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C60" t="str">
-        <v>0 ms</v>
+        <v>1485 ms</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Search Functionality (20 Cases) Search: empty query should handle search for empty query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: scientific notation budget should prevent invalid project creation: scientific notation budget</v>
       </c>
       <c r="B61" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C61" t="str">
-        <v>1 ms</v>
+        <v>1599 ms</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Search Functionality (20 Cases) Search: whitespace around query should handle search for whitespace around query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: NaN budget should prevent invalid project creation: NaN budget</v>
       </c>
       <c r="B62" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C62" t="str">
-        <v>0 ms</v>
+        <v>1506 ms</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Search Functionality (20 Cases) Search: emoji query should handle search for emoji query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: Infinity budget should prevent invalid project creation: Infinity budget</v>
       </c>
       <c r="B63" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C63" t="str">
-        <v>0 ms</v>
+        <v>1496 ms</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Search Functionality (20 Cases) Search: insanely long query should handle search for insanely long query</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in title should prevent invalid project creation: special characters in title</v>
       </c>
       <c r="B64" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C64" t="str">
-        <v>1 ms</v>
+        <v>1713 ms</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 1 should handle search for SQL injection payload 1</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: special characters in desc should prevent invalid project creation: special characters in desc</v>
       </c>
       <c r="B65" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C65" t="str">
-        <v>0 ms</v>
+        <v>1584 ms</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Search Functionality (20 Cases) Search: SQL injection payload 2 should handle search for SQL injection payload 2</v>
+        <v>Project Creation Validation (25 Cases) Project Creation: symbols in text should prevent invalid project creation: symbols in text</v>
       </c>
       <c r="B66" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C66" t="str">
-        <v>0 ms</v>
+        <v>1736 ms</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS payload should handle search for XSS payload</v>
+        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
       </c>
       <c r="B67" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C67" t="str">
-        <v>0 ms</v>
+        <v>1503 ms</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Search Functionality (20 Cases) Search: XSS img payload should handle search for XSS img payload</v>
+        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
       </c>
       <c r="B68" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C68" t="str">
-        <v>0 ms</v>
+        <v>1517 ms</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Search Functionality (20 Cases) Search: extremely long query should handle search for extremely long query</v>
+        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
       </c>
       <c r="B69" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C69" t="str">
-        <v>0 ms</v>
+        <v>1298 ms</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Search Functionality (20 Cases) Search: japanese characters should handle search for japanese characters</v>
+        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
       </c>
       <c r="B70" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C70" t="str">
-        <v>1 ms</v>
+        <v>1328 ms</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Search Functionality (20 Cases) Search: russian characters should handle search for russian characters</v>
+        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
       </c>
       <c r="B71" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C71" t="str">
-        <v>0 ms</v>
+        <v>1351 ms</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Search Functionality (20 Cases) Search: arabic characters should handle search for arabic characters</v>
+        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
       </c>
       <c r="B72" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C72" t="str">
-        <v>0 ms</v>
+        <v>1313 ms</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search Functionality (20 Cases) Search: single character should handle search for single character</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty amount should prevent invalid proposal: empty amount</v>
       </c>
       <c r="B73" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C73" t="str">
-        <v>0 ms</v>
+        <v>2792 ms</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search Functionality (20 Cases) Search: numeric query should handle search for numeric query</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: zero amount should prevent invalid proposal: zero amount</v>
       </c>
       <c r="B74" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C74" t="str">
-        <v>0 ms</v>
+        <v>2555 ms</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search Functionality (20 Cases) Search: special characters should handle search for special characters</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: negative amount should prevent invalid proposal: negative amount</v>
       </c>
       <c r="B75" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C75" t="str">
-        <v>1 ms</v>
+        <v>2521 ms</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Proposal Workflow End-to-End client creates project, freelancer proposes, client accepts concurrently</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: insanely high amount should prevent invalid proposal: insanely high amount</v>
       </c>
       <c r="B76" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C76" t="str">
-        <v>16476 ms</v>
+        <v>2551 ms</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Global Exhaustive Smoke Test should render Dashboard and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: non-numeric amount should prevent invalid proposal: non-numeric amount</v>
       </c>
       <c r="B77" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C77" t="str">
-        <v>1 ms</v>
+        <v>2619 ms</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Global Exhaustive Smoke Test should render Projects Listing and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: empty cover letter should prevent invalid proposal: empty cover letter</v>
       </c>
       <c r="B78" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C78" t="str">
-        <v>1 ms</v>
+        <v>2594 ms</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Global Exhaustive Smoke Test should render Messages and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too short should prevent invalid proposal: cover letter too short</v>
       </c>
       <c r="B79" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C79" t="str">
-        <v>0 ms</v>
+        <v>2828 ms</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Global Exhaustive Smoke Test should render Wallet and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: cover letter too long should prevent invalid proposal: cover letter too long</v>
       </c>
       <c r="B80" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C80" t="str">
-        <v>0 ms</v>
+        <v>2625 ms</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Global Exhaustive Smoke Test should render Profile and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: XSS in cover letter should prevent invalid proposal: XSS in cover letter</v>
       </c>
       <c r="B81" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C81" t="str">
-        <v>1 ms</v>
+        <v>2582 ms</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Global Exhaustive Smoke Test should render Settings and verify buttons</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: SQL inject in cover letter should prevent invalid proposal: SQL inject in cover letter</v>
       </c>
       <c r="B82" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C82" t="str">
-        <v>0 ms</v>
+        <v>2553 ms</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Projects &amp; Kanban should create, filter, and view project details</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: decimal amount should prevent invalid proposal: decimal amount</v>
       </c>
       <c r="B83" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C83" t="str">
-        <v>10878 ms</v>
+        <v>2511 ms</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Wallet should view wallet page</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: NaN amount should prevent invalid proposal: NaN amount</v>
       </c>
       <c r="B84" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C84" t="str">
-        <v>11338 ms</v>
+        <v>2532 ms</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Wallet should withdraw funds and show toast</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: Infinity amount should prevent invalid proposal: Infinity amount</v>
       </c>
       <c r="B85" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C85" t="str">
-        <v>10647 ms</v>
+        <v>2511 ms</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Wallet should export CSV</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace cover letter should prevent invalid proposal: whitespace cover letter</v>
       </c>
       <c r="B86" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C86" t="str">
-        <v>10660 ms</v>
+        <v>2558 ms</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Authentication &amp; Onboarding should navigate onboarding and login</v>
+        <v>Proposals &amp; Bidding (15 Cases) Proposal: whitespace amount should prevent invalid proposal: whitespace amount</v>
       </c>
       <c r="B87" t="str">
         <v>PASSED</v>
       </c>
       <c r="C87" t="str">
-        <v>8690 ms</v>
+        <v>2580 ms</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Freelancer Workflow (Empty State) should verify all buttons in empty state for freelancer</v>
+        <v>Authentication &amp; Onboarding should navigate onboarding and login</v>
       </c>
       <c r="B88" t="str">
         <v>PASSED</v>
       </c>
       <c r="C88" t="str">
-        <v>4104 ms</v>
+        <v>5129 ms</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Communication should view messages page empty state</v>
+        <v>Freelancer Workflow (Empty State) should verify all buttons in empty state for freelancer</v>
       </c>
       <c r="B89" t="str">
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="C89" t="str">
-        <v>11268 ms</v>
+        <v>3432 ms</v>
       </c>
     </row>
   </sheetData>
